--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/1906-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/1906-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45D0F419-A46B-4251-90B5-D7C60892B0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5046CD74-690C-4A3D-B8E9-45C6A078B94B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{E170AE7F-FAC2-4B4E-B4C6-86D7EB38279A}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{FB94F904-E615-4DFB-99DE-AD2E2C1ABBEF}"/>
   </bookViews>
   <sheets>
     <sheet name="1906-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1487,25 +1487,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D0CCFB94-2F5E-429E-B35A-006941C544CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D110260-6D6A-4258-9298-EBCC0DA43C10}">
   <dimension ref="A1:X61"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="9.125" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1575,7 +1575,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1627,7 +1627,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1695,7 +1695,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1841,7 +1841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1915,7 +1915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2024</v>
       </c>
@@ -1987,7 +1987,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2061,7 +2061,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="16" t="s">
         <v>29</v>
       </c>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2023</v>
       </c>
@@ -2281,7 +2281,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>29</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>1.1299999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>29</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>29</v>
       </c>
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="38">
         <v>2022</v>
       </c>
@@ -2575,7 +2575,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="16" t="s">
         <v>29</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="16" t="s">
         <v>29</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2021</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2020</v>
       </c>
@@ -3163,7 +3163,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3311,7 +3311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3385,7 +3385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2019</v>
       </c>
@@ -3457,7 +3457,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="11" t="s">
         <v>29</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>5.17</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="11" t="s">
         <v>29</v>
       </c>
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2018</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>4.17</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2017</v>
       </c>
@@ -3749,7 +3749,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2016</v>
       </c>
@@ -3821,7 +3821,7 @@
         <v>8.77</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2015</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2014</v>
       </c>
@@ -3965,7 +3965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2013</v>
       </c>
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2012</v>
       </c>
@@ -4109,7 +4109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>2011</v>
       </c>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2010</v>
       </c>
@@ -4253,7 +4253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>2009</v>
       </c>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2008</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>2007</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>2006</v>
       </c>
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>2005</v>
       </c>
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>2004</v>
       </c>
@@ -4685,7 +4685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>2003</v>
       </c>
@@ -4757,7 +4757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>2002</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>2001</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>2000</v>
       </c>
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="36">
         <v>1999</v>
       </c>
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1998</v>
       </c>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <v>1997</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1996</v>
       </c>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
         <v>1995</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38">
         <v>1994</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="36">
         <v>1993</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="38">
         <v>1992</v>
       </c>
@@ -5549,7 +5549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="36">
         <v>1991</v>
       </c>
@@ -5621,7 +5621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A59" s="38">
         <v>1990</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A60" s="36">
         <v>1989</v>
       </c>
@@ -5765,7 +5765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A61" s="38" t="s">
         <v>49</v>
       </c>
